--- a/data/trans_orig/IP1003-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17973</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>120419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132072</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132595</t>
+          <t>132736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144441</t>
+          <t>144505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258119</t>
+          <t>257237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273830</t>
+          <t>273106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35671</t>
+          <t>35286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178801</t>
+          <t>178830</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188223</t>
+          <t>188503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189001</t>
+          <t>189354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202056</t>
+          <t>202053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371634</t>
+          <t>372019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387365</t>
+          <t>387422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126738</t>
+          <t>126421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134398</t>
+          <t>134324</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135071</t>
+          <t>135183</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144579</t>
+          <t>144475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264924</t>
+          <t>265126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277624</t>
+          <t>276979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>30809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191312</t>
+          <t>191243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202729</t>
+          <t>202783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189434</t>
+          <t>188892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200533</t>
+          <t>200516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>385530</t>
+          <t>386330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401206</t>
+          <t>401466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>51436</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40194</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61202</t>
+          <t>60760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76829</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107294</t>
+          <t>107716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>629701</t>
+          <t>629585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>648912</t>
+          <t>650175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>661498</t>
+          <t>661940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682506</t>
+          <t>683542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296427</t>
+          <t>1296005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1326892</t>
+          <t>1326276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119879</t>
+          <t>120389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130565</t>
+          <t>131056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141240</t>
+          <t>140660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149483</t>
+          <t>149581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>263482</t>
+          <t>265189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278337</t>
+          <t>278266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33022</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193938</t>
+          <t>193776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202028</t>
+          <t>202023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196633</t>
+          <t>197149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210117</t>
+          <t>210531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394354</t>
+          <t>393070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410296</t>
+          <t>410045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141131</t>
+          <t>141942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150612</t>
+          <t>150561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151945</t>
+          <t>152184</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161002</t>
+          <t>161138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297985</t>
+          <t>297806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310024</t>
+          <t>309672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194149</t>
+          <t>194587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204927</t>
+          <t>205142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187481</t>
+          <t>188162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199855</t>
+          <t>199801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386099</t>
+          <t>387152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402644</t>
+          <t>402952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,47 +4067,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35045</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>56959</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>6,1%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34688</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>57298</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65827</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>95580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>663212</t>
+          <t>661966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>682046</t>
+          <t>681400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,47 +4180,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>702474</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>691183</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>713097</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>93,9%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>702474</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>690844</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>713454</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1359938</t>
+          <t>1358863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1388616</t>
+          <t>1388891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123346</t>
+          <t>123623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131839</t>
+          <t>131668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132811</t>
+          <t>133361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143326</t>
+          <t>144027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260385</t>
+          <t>260447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273529</t>
+          <t>273486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22657</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20009</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36238</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189488</t>
+          <t>189923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199942</t>
+          <t>200190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201702</t>
+          <t>200993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>214206</t>
+          <t>214104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395368</t>
+          <t>395025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411597</t>
+          <t>411404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145726</t>
+          <t>145145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153373</t>
+          <t>153339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155587</t>
+          <t>155809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164287</t>
+          <t>164169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304940</t>
+          <t>304315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315351</t>
+          <t>315625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26282</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189727</t>
+          <t>190325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201310</t>
+          <t>201609</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192397</t>
+          <t>191931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201548</t>
+          <t>201677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386874</t>
+          <t>386828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>400869</t>
+          <t>401141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>41695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>50237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86083</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>660831</t>
+          <t>662676</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>680525</t>
+          <t>680760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694678</t>
+          <t>694607</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>715621</t>
+          <t>715192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1363132</t>
+          <t>1363683</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1390733</t>
+          <t>1391669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15247</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>15319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32236</t>
+          <t>32077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102033</t>
+          <t>102069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111819</t>
+          <t>111404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118077</t>
+          <t>117643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132764</t>
+          <t>132720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224454</t>
+          <t>224613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241506</t>
+          <t>241371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50202</t>
+          <t>49925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167888</t>
+          <t>169244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181582</t>
+          <t>181483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220578</t>
+          <t>219272</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239123</t>
+          <t>239147</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395346</t>
+          <t>395623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415820</t>
+          <t>418228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177324</t>
+          <t>176496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>186355</t>
+          <t>186003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165439</t>
+          <t>166485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178928</t>
+          <t>179286</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346684</t>
+          <t>348091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363090</t>
+          <t>363342</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155207</t>
+          <t>154982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164363</t>
+          <t>164175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157434</t>
+          <t>157735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172301</t>
+          <t>172328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316282</t>
+          <t>316478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333636</t>
+          <t>334020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47281</t>
+          <t>50068</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>79927</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119073</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>616603</t>
+          <t>613816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>637322</t>
+          <t>636468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680125</t>
+          <t>680250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710985</t>
+          <t>710884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1304989</t>
+          <t>1305475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341278</t>
+          <t>1344847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1003-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20667</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11877</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7140</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18307</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7168</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18394</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13502</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8572</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20341</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>33887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>139575</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>132410</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144211</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>126849</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>120419</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131586</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>120332</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131558</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>139575</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>132736</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144505</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257237</t>
+          <t>257916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273106</t>
+          <t>272922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10615</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23314</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10974</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6660</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16333</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6937</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17305</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10089</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22788</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35286</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>196243</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>188828</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>201527</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>184189</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>178830</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>188503</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>177858</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>188226</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>196243</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>189354</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>202053</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>372019</t>
+          <t>372009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387422</t>
+          <t>387522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5415</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14908</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6437</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3493</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11396</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11026</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8963</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5182</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14474</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22348</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1527,67 +1527,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>140694</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>134749</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>144242</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>131380</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>126421</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134324</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126791</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134585</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140694</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>135183</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>144475</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,01%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265126</t>
+          <t>264910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276979</t>
+          <t>277209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11604</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7361</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18862</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11351</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6532</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18072</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6690</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11604</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7308</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18932</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30809</t>
+          <t>32707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>196220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>188962</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>200463</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>197964</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>191243</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>202783</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>191842</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>202625</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>196220</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>188892</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>200516</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386330</t>
+          <t>384432</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401466</t>
+          <t>400935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39235</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60973</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>40639</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30846</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51436</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31291</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50830</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>49967</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>39158</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>60760</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77445</t>
+          <t>76611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107716</t>
+          <t>106770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>672733</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>661727</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>683465</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>957</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>640382</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>629585</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>650175</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>630191</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>649730</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>672733</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>661940</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>683542</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296005</t>
+          <t>1296951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1326276</t>
+          <t>1327110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3426</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11791</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9936</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5335</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16002</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16070</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7007</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3517</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12438</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>25303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>146091</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>141307</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>149672</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>126455</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>120389</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131056</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>120321</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>130953</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>146091</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>140660</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>149581</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265189</t>
+          <t>264186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278266</t>
+          <t>278548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17999</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11634</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25089</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6664</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3375</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11622</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12045</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>1,64%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17999</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11446</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24828</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>203978</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>196888</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>210343</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>198734</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>193776</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>202023</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>193353</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202034</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>98,36%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>203978</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>197149</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>210531</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>94,84%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>603</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393070</t>
+          <t>393838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410045</t>
+          <t>409984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8462</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4621</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13823</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7072</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3651</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12270</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3573</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12257</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8462</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13801</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157523</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>152162</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>147140</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>141942</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150561</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>141955</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150639</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157523</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>152184</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>161138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,9%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297806</t>
+          <t>297138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309672</t>
+          <t>309781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154212</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154212</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154212</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12200</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7386</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18638</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9517</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5158</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15713</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5370</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16351</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12200</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7281</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18920</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>194882</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>188444</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>199696</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200783</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>194587</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>205142</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>193949</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>204930</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,47%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>194882</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>188162</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>199801</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>387152</t>
+          <t>387141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402952</t>
+          <t>402215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35965</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>57637</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33189</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24901</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44335</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24394</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43668</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>35045</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>56959</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65552</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95580</t>
+          <t>94771</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>702474</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>690505</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>712177</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>673112</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>661966</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>681400</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>662633</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>681907</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>702474</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>691183</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>713097</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1358863</t>
+          <t>1359672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1388891</t>
+          <t>1389249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706301</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706301</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706301</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8723</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14652</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4724</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10084</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1769</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10811</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8723</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4049</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14715</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>139353</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>133424</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>143396</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>123623</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131668</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131938</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>139353</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>133361</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144027</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260447</t>
+          <t>260157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273486</t>
+          <t>273655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15717</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9809</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22772</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11592</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7057</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17324</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17935</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15717</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10255</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23366</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>208642</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>201587</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>214550</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>195655</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>189923</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>200190</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>189312</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>200334</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>208642</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>200993</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>214104</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395025</t>
+          <t>395114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411404</t>
+          <t>412190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5308,67 +5308,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2477</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11697</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>5723</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2658</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10852</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2765</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10738</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10864</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>160783</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154976</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164196</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>150274</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>145145</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>153339</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>145259</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153232</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>160783</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>155809</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164169</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304315</t>
+          <t>304767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315625</t>
+          <t>315670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8270</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10092</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5811</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17095</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16146</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8270</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4059</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13805</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26328</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>197466</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>191435</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201462</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>197328</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190325</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>201609</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>191274</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>202076</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>197466</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>191931</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>201677</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386828</t>
+          <t>386414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401141</t>
+          <t>401237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,107 +5989,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29165</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49869</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>32132</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23611</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41695</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23158</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42850</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>58078</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>85840</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>38600</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>29652</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>50237</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>70732</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>57546</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>85532</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6102,107 +6102,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>706244</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>694975</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>715679</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>672239</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>662676</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680760</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>661521</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>681213</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,44%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1378483</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1363375</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1391137</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>94,08%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>706244</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>694607</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>715192</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1378483</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1363683</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1391669</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11890</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6194</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21172</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9462</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15211</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22118</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32077</t>
+          <t>32056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>113064</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>103782</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>118760</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>107818</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>102069</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>111404</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126760</t>
+          <t>110844</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117643</t>
+          <t>105493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132720</t>
+          <t>115171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>234578</t>
+          <t>223907</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224613</t>
+          <t>213969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241371</t>
+          <t>231291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124954</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124954</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124954</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256690</t>
+          <t>246025</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256690</t>
+          <t>246025</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256690</t>
+          <t>246025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21950</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15138</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31624</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14615</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9029</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21268</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>26950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49925</t>
+          <t>47328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>215256</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205582</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>222068</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>175897</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>169244</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181483</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>231103</t>
+          <t>169561</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219272</t>
+          <t>161982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239147</t>
+          <t>174729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>407001</t>
+          <t>384816</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395623</t>
+          <t>374291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>418228</t>
+          <t>394669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10896</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5664</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18703</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5959</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2751</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12258</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156848</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149041</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>162080</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>182795</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>176496</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>186003</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>173658</t>
+          <t>149075</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166485</t>
+          <t>143098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179286</t>
+          <t>152416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>356454</t>
+          <t>305922</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348091</t>
+          <t>296326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363342</t>
+          <t>312357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167744</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167744</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167744</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188754</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188754</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188754</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184494</t>
+          <t>155334</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184494</t>
+          <t>155334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184494</t>
+          <t>155334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>373249</t>
+          <t>323078</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>373249</t>
+          <t>323078</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>373249</t>
+          <t>323078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13742</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8198</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21186</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6566</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3162</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12355</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32098</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155634</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148190</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>161178</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>160771</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>154982</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164175</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166021</t>
+          <t>159760</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157735</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172328</t>
+          <t>163449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326793</t>
+          <t>315395</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316478</t>
+          <t>307219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334020</t>
+          <t>321965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167337</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167337</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>335918</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>335918</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>335918</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45376</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72397</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36603</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27416</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50068</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79927</t>
+          <t>50580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>96599</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79215</t>
+          <t>79789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118587</t>
+          <t>113760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>640801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>626883</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>653904</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>627281</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>613816</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>636468</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>697542</t>
+          <t>589239</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680250</t>
+          <t>576779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710884</t>
+          <t>598125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1324824</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1305475</t>
+          <t>1212879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1344847</t>
+          <t>1246850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663884</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663884</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663884</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>627359</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>627359</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>627359</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1424062</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1424062</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1424062</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
